--- a/Standard_Chart_filled.xlsx
+++ b/Standard_Chart_filled.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11490" firstSheet="4" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="7455" firstSheet="7" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="GuidePin" sheetId="1" r:id="rId1"/>
@@ -21,29 +21,15 @@
     <sheet name="EjectorGuidePin" sheetId="7" r:id="rId7"/>
     <sheet name="EjectorGuideBush" sheetId="8" r:id="rId8"/>
     <sheet name="LocatingRing" sheetId="9" r:id="rId9"/>
+    <sheet name="PlateThickness" sheetId="10" r:id="rId10"/>
+    <sheet name="MachiningProcess" sheetId="11" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="46">
   <si>
     <t>Type</t>
   </si>
@@ -51,39 +37,45 @@
     <t>Diameter C</t>
   </si>
   <si>
+    <t>Diameter F</t>
+  </si>
+  <si>
+    <t>Diameter G</t>
+  </si>
+  <si>
+    <t>Length</t>
+  </si>
+  <si>
+    <t>Wgt (kgs)</t>
+  </si>
+  <si>
+    <t>MTL C</t>
+  </si>
+  <si>
+    <t>Lathe time (mins)</t>
+  </si>
+  <si>
+    <t>Lathe Cost</t>
+  </si>
+  <si>
+    <t>Hard Cost</t>
+  </si>
+  <si>
+    <t>Grind Cost</t>
+  </si>
+  <si>
+    <t>Total Cost</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>Diameter D</t>
   </si>
   <si>
     <t>Diameter E</t>
   </si>
   <si>
-    <t>Length</t>
-  </si>
-  <si>
-    <t>Wgt (kgs)</t>
-  </si>
-  <si>
-    <t>MTL C</t>
-  </si>
-  <si>
-    <t>Lathe time (mins)</t>
-  </si>
-  <si>
-    <t>Lathe Cost</t>
-  </si>
-  <si>
-    <t>Hard Cost</t>
-  </si>
-  <si>
-    <t>Grind Cost</t>
-  </si>
-  <si>
-    <t>Total Cost</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>B</t>
   </si>
   <si>
@@ -99,46 +91,82 @@
     <t>Rate</t>
   </si>
   <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>M6</t>
+  </si>
+  <si>
+    <t>M8</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>M12</t>
+  </si>
+  <si>
+    <t>M16</t>
+  </si>
+  <si>
     <t>W</t>
   </si>
   <si>
     <t>T</t>
   </si>
   <si>
-    <t>Diameter F</t>
-  </si>
-  <si>
-    <t>Diameter G</t>
-  </si>
-  <si>
-    <t>M3</t>
-  </si>
-  <si>
-    <t>M4</t>
-  </si>
-  <si>
-    <t>M5</t>
-  </si>
-  <si>
-    <t>M6</t>
-  </si>
-  <si>
-    <t>M8</t>
-  </si>
-  <si>
-    <t>M10</t>
-  </si>
-  <si>
-    <t>M12</t>
-  </si>
-  <si>
-    <t>M16</t>
+    <t>thickness</t>
   </si>
   <si>
     <t>cost</t>
   </si>
   <si>
-    <t>thickness</t>
+    <t>Thickness</t>
+  </si>
+  <si>
+    <t>48-60</t>
+  </si>
+  <si>
+    <t>Collar counter</t>
+  </si>
+  <si>
+    <t>30-48</t>
+  </si>
+  <si>
+    <t>24-30</t>
+  </si>
+  <si>
+    <t>16-24</t>
+  </si>
+  <si>
+    <t>Boring</t>
+  </si>
+  <si>
+    <t>Roughing</t>
+  </si>
+  <si>
+    <t>Setting cost</t>
+  </si>
+  <si>
+    <t>U-drill</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Time (min)</t>
+  </si>
+  <si>
+    <t>Bore Diameter</t>
+  </si>
+  <si>
+    <t>Process</t>
   </si>
 </sst>
 </file>
@@ -187,7 +215,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -195,11 +223,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -207,6 +250,24 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -531,10 +592,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -1070,6 +1131,642 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H37"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.42578125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="17" style="8" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="9">
+        <v>24</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="7">
+        <v>3</v>
+      </c>
+      <c r="E2" s="9">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="9">
+        <v>24</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="7">
+        <v>5</v>
+      </c>
+      <c r="E3" s="9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="9">
+        <v>24</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="7">
+        <v>10</v>
+      </c>
+      <c r="E4" s="9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="9">
+        <v>30</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="7">
+        <v>3</v>
+      </c>
+      <c r="E5" s="9">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="9">
+        <v>30</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="7">
+        <v>5</v>
+      </c>
+      <c r="E6" s="9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="9">
+        <v>30</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="7">
+        <v>10</v>
+      </c>
+      <c r="E7" s="9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="9">
+        <v>42</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="9"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="9">
+        <v>42</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="9"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="9">
+        <v>42</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="9"/>
+      <c r="H10" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="9">
+        <v>24</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="7">
+        <v>5</v>
+      </c>
+      <c r="E11" s="7">
+        <v>50</v>
+      </c>
+      <c r="H11" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="9">
+        <v>24</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="7">
+        <v>10</v>
+      </c>
+      <c r="E12" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="9">
+        <v>24</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="7">
+        <v>15</v>
+      </c>
+      <c r="E13" s="7">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="9">
+        <v>30</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="7">
+        <v>5</v>
+      </c>
+      <c r="E14" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="9">
+        <v>30</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="7">
+        <v>10</v>
+      </c>
+      <c r="E15" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="9">
+        <v>30</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="7">
+        <v>15</v>
+      </c>
+      <c r="E16" s="7">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="9">
+        <v>42</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="9">
+        <v>42</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="9">
+        <v>42</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="9">
+        <v>24</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="7">
+        <v>5</v>
+      </c>
+      <c r="E20" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="9">
+        <v>24</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="7">
+        <v>7</v>
+      </c>
+      <c r="E21" s="7">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="9">
+        <v>24</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="7">
+        <v>10</v>
+      </c>
+      <c r="E22" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="9">
+        <v>30</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="7">
+        <v>5</v>
+      </c>
+      <c r="E23" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="9">
+        <v>30</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="7">
+        <v>7</v>
+      </c>
+      <c r="E24" s="7">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="9">
+        <v>30</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" s="7">
+        <v>10</v>
+      </c>
+      <c r="E25" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="9">
+        <v>42</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="9">
+        <v>42</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="9">
+        <v>42</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="9">
+        <v>24</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="7">
+        <v>5</v>
+      </c>
+      <c r="E29" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="9">
+        <v>24</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="7">
+        <v>5</v>
+      </c>
+      <c r="E30" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="9">
+        <v>24</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" s="7">
+        <v>5</v>
+      </c>
+      <c r="E31" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="9">
+        <v>30</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" s="7">
+        <v>5</v>
+      </c>
+      <c r="E32" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="9">
+        <v>30</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33" s="7">
+        <v>5</v>
+      </c>
+      <c r="E33" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="9">
+        <v>30</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="7">
+        <v>5</v>
+      </c>
+      <c r="E34" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="9">
+        <v>42</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="9">
+        <v>42</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" s="9">
+        <v>42</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1094,10 +1791,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -1610,7 +2307,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B16">
         <v>25</v>
@@ -1624,7 +2321,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B17">
         <v>25</v>
@@ -1638,7 +2335,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B18">
         <v>25</v>
@@ -1652,7 +2349,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B19">
         <v>35</v>
@@ -1666,7 +2363,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <v>35</v>
@@ -1680,7 +2377,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B21">
         <v>35</v>
@@ -1694,7 +2391,7 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B22">
         <v>35</v>
@@ -1708,7 +2405,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B23">
         <v>35</v>
@@ -1722,7 +2419,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B24">
         <v>47</v>
@@ -1760,7 +2457,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B25">
         <v>47</v>
@@ -1774,7 +2471,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B26">
         <v>47</v>
@@ -1788,7 +2485,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B27">
         <v>47</v>
@@ -1802,7 +2499,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -1816,19 +2513,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2077,18 +2774,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2">
         <v>10</v>
@@ -2099,7 +2796,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3">
         <v>15</v>
@@ -2110,7 +2807,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4">
         <v>20</v>
@@ -2121,7 +2818,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5">
         <v>30</v>
@@ -2132,7 +2829,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>40</v>
@@ -2143,7 +2840,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7">
         <v>10</v>
@@ -2154,7 +2851,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8">
         <v>15</v>
@@ -2165,7 +2862,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>20</v>
@@ -2176,7 +2873,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10">
         <v>30</v>
@@ -2187,7 +2884,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>40</v>
@@ -2198,7 +2895,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12">
         <v>50</v>
@@ -2209,7 +2906,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B13">
         <v>60</v>
@@ -2220,7 +2917,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B14">
         <v>10</v>
@@ -2231,7 +2928,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B15">
         <v>15</v>
@@ -2242,7 +2939,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B16">
         <v>20</v>
@@ -2253,7 +2950,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B17">
         <v>30</v>
@@ -2264,7 +2961,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B18">
         <v>40</v>
@@ -2275,7 +2972,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B19">
         <v>50</v>
@@ -2286,7 +2983,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B20">
         <v>60</v>
@@ -2297,7 +2994,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B21">
         <v>70</v>
@@ -2308,7 +3005,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B22">
         <v>10</v>
@@ -2319,7 +3016,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B23">
         <v>15</v>
@@ -2330,7 +3027,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B24">
         <v>20</v>
@@ -2341,7 +3038,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B25">
         <v>30</v>
@@ -2352,7 +3049,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B26">
         <v>40</v>
@@ -2363,7 +3060,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B27">
         <v>50</v>
@@ -2374,7 +3071,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B28">
         <v>60</v>
@@ -2385,7 +3082,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B29">
         <v>70</v>
@@ -2396,7 +3093,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B30">
         <v>80</v>
@@ -2407,7 +3104,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B31">
         <v>90</v>
@@ -2418,7 +3115,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B32">
         <v>100</v>
@@ -2429,7 +3126,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B33">
         <v>120</v>
@@ -2440,7 +3137,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B34">
         <v>140</v>
@@ -2451,7 +3148,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B35">
         <v>10</v>
@@ -2462,7 +3159,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B36">
         <v>15</v>
@@ -2473,7 +3170,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B37">
         <v>20</v>
@@ -2484,7 +3181,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B38">
         <v>30</v>
@@ -2495,7 +3192,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B39">
         <v>40</v>
@@ -2506,7 +3203,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B40">
         <v>50</v>
@@ -2517,7 +3214,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B41">
         <v>60</v>
@@ -2528,7 +3225,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B42">
         <v>70</v>
@@ -2539,7 +3236,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B43">
         <v>80</v>
@@ -2550,7 +3247,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B44">
         <v>90</v>
@@ -2561,7 +3258,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B45">
         <v>100</v>
@@ -2572,7 +3269,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B46">
         <v>120</v>
@@ -2583,7 +3280,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B47">
         <v>140</v>
@@ -2594,7 +3291,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B48">
         <v>150</v>
@@ -2605,7 +3302,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B49">
         <v>10</v>
@@ -2616,7 +3313,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B50">
         <v>15</v>
@@ -2627,7 +3324,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B51">
         <v>20</v>
@@ -2638,7 +3335,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B52">
         <v>30</v>
@@ -2649,7 +3346,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B53">
         <v>40</v>
@@ -2660,7 +3357,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B54">
         <v>50</v>
@@ -2671,7 +3368,7 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B55">
         <v>60</v>
@@ -2682,7 +3379,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B56">
         <v>70</v>
@@ -2693,7 +3390,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B57">
         <v>80</v>
@@ -2704,7 +3401,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B58">
         <v>90</v>
@@ -2715,7 +3412,7 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B59">
         <v>100</v>
@@ -2726,7 +3423,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B60">
         <v>120</v>
@@ -2737,7 +3434,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B61">
         <v>140</v>
@@ -2748,7 +3445,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B62">
         <v>150</v>
@@ -2759,7 +3456,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B63">
         <v>10</v>
@@ -2767,7 +3464,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B64">
         <v>15</v>
@@ -2778,7 +3475,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B65">
         <v>20</v>
@@ -2789,7 +3486,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B66">
         <v>30</v>
@@ -2800,7 +3497,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B67">
         <v>40</v>
@@ -2811,7 +3508,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B68">
         <v>50</v>
@@ -2822,7 +3519,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B69">
         <v>60</v>
@@ -2833,7 +3530,7 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B70">
         <v>70</v>
@@ -2844,7 +3541,7 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B71">
         <v>80</v>
@@ -2855,7 +3552,7 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B72">
         <v>90</v>
@@ -2866,7 +3563,7 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B73">
         <v>100</v>
@@ -2877,7 +3574,7 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B74">
         <v>120</v>
@@ -2888,7 +3585,7 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B75">
         <v>140</v>
@@ -2899,7 +3596,7 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B76">
         <v>150</v>
@@ -2910,7 +3607,7 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B77">
         <v>180</v>
@@ -2921,7 +3618,7 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B78">
         <v>200</v>
@@ -2932,7 +3629,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B79">
         <v>10</v>
@@ -2940,7 +3637,7 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B80">
         <v>15</v>
@@ -2948,7 +3645,7 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B81">
         <v>20</v>
@@ -2959,7 +3656,7 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B82">
         <v>30</v>
@@ -2970,7 +3667,7 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B83">
         <v>40</v>
@@ -2981,7 +3678,7 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B84">
         <v>50</v>
@@ -2992,7 +3689,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B85">
         <v>60</v>
@@ -3003,7 +3700,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B86">
         <v>70</v>
@@ -3014,7 +3711,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B87">
         <v>80</v>
@@ -3025,7 +3722,7 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B88">
         <v>90</v>
@@ -3036,7 +3733,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B89">
         <v>100</v>
@@ -3047,7 +3744,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B90">
         <v>120</v>
@@ -3058,7 +3755,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B91">
         <v>140</v>
@@ -3069,7 +3766,7 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B92">
         <v>150</v>
@@ -3080,7 +3777,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B93">
         <v>180</v>
@@ -3091,7 +3788,7 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B94">
         <v>200</v>
@@ -3102,7 +3799,7 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B95">
         <v>210</v>
@@ -3113,7 +3810,7 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B96">
         <v>220</v>
@@ -3124,7 +3821,7 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B97">
         <v>230</v>
@@ -3135,7 +3832,7 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B98">
         <v>240</v>
@@ -3146,7 +3843,7 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B99">
         <v>250</v>
@@ -3157,7 +3854,7 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B100">
         <v>260</v>
@@ -3168,7 +3865,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B101">
         <v>270</v>
@@ -3179,7 +3876,7 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B102">
         <v>280</v>
@@ -3190,7 +3887,7 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B103">
         <v>290</v>
@@ -3201,7 +3898,7 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B104">
         <v>300</v>
@@ -3225,16 +3922,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -3294,16 +3991,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -3531,13 +4228,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -3555,13 +4252,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -3579,13 +4276,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">

--- a/Standard_Chart_filled.xlsx
+++ b/Standard_Chart_filled.xlsx
@@ -1,35 +1,54 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30431"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{354A867E-E3E9-4EF4-A70F-773F932181E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="7455" firstSheet="7" activeTab="10"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="7455" firstSheet="10" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GuidePin" sheetId="1" r:id="rId1"/>
     <sheet name="GuideBush" sheetId="2" r:id="rId2"/>
     <sheet name="ReturnPin" sheetId="3" r:id="rId3"/>
     <sheet name="Bolts" sheetId="4" r:id="rId4"/>
-    <sheet name="DowellingSleeve" sheetId="5" r:id="rId5"/>
-    <sheet name="HookStrip" sheetId="6" r:id="rId6"/>
-    <sheet name="EjectorGuidePin" sheetId="7" r:id="rId7"/>
-    <sheet name="EjectorGuideBush" sheetId="8" r:id="rId8"/>
-    <sheet name="LocatingRing" sheetId="9" r:id="rId9"/>
-    <sheet name="PlateThickness" sheetId="10" r:id="rId10"/>
-    <sheet name="MachiningProcess" sheetId="11" r:id="rId11"/>
+    <sheet name="Cavityhousingdrilling" sheetId="12" r:id="rId5"/>
+    <sheet name="CavityInsertDrilling" sheetId="13" r:id="rId6"/>
+    <sheet name="DowellingSleeve" sheetId="5" r:id="rId7"/>
+    <sheet name="HookStrip" sheetId="6" r:id="rId8"/>
+    <sheet name="EjectorGuidePin" sheetId="7" r:id="rId9"/>
+    <sheet name="EjectorGuideBush" sheetId="8" r:id="rId10"/>
+    <sheet name="LocatingRing" sheetId="9" r:id="rId11"/>
+    <sheet name="PlateThickness" sheetId="10" r:id="rId12"/>
+    <sheet name="BoringProcess" sheetId="11" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="48">
   <si>
     <t>Type</t>
   </si>
@@ -115,6 +134,21 @@
     <t>M16</t>
   </si>
   <si>
+    <t>Diameter</t>
+  </si>
+  <si>
+    <t>Thickness</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>24-30</t>
+  </si>
+  <si>
+    <t>38-48</t>
+  </si>
+  <si>
     <t>W</t>
   </si>
   <si>
@@ -127,53 +161,44 @@
     <t>cost</t>
   </si>
   <si>
-    <t>Thickness</t>
+    <t>Process</t>
+  </si>
+  <si>
+    <t>Bore Diameter</t>
+  </si>
+  <si>
+    <t>Time (min)</t>
+  </si>
+  <si>
+    <t>U-drill</t>
+  </si>
+  <si>
+    <t>16-24</t>
+  </si>
+  <si>
+    <t>30-48</t>
   </si>
   <si>
     <t>48-60</t>
   </si>
   <si>
+    <t>Setting cost</t>
+  </si>
+  <si>
+    <t>Roughing</t>
+  </si>
+  <si>
+    <t>Boring</t>
+  </si>
+  <si>
     <t>Collar counter</t>
-  </si>
-  <si>
-    <t>30-48</t>
-  </si>
-  <si>
-    <t>24-30</t>
-  </si>
-  <si>
-    <t>16-24</t>
-  </si>
-  <si>
-    <t>Boring</t>
-  </si>
-  <si>
-    <t>Roughing</t>
-  </si>
-  <si>
-    <t>Setting cost</t>
-  </si>
-  <si>
-    <t>U-drill</t>
-  </si>
-  <si>
-    <t>Cost</t>
-  </si>
-  <si>
-    <t>Time (min)</t>
-  </si>
-  <si>
-    <t>Bore Diameter</t>
-  </si>
-  <si>
-    <t>Process</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -242,7 +267,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -256,10 +281,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -569,9 +591,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -584,7 +606,7 @@
     <col min="11" max="11" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -622,7 +644,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -660,7 +682,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -698,7 +720,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -736,7 +758,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -774,7 +796,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -812,7 +834,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -850,7 +872,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -888,7 +910,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -926,7 +948,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -964,7 +986,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1002,7 +1024,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1016,7 +1038,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1030,7 +1052,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1044,7 +1066,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -1061,7 +1083,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -1078,7 +1100,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -1095,7 +1117,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -1112,7 +1134,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -1135,48 +1157,22 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="3" width="12" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>25.4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>76</v>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1185,9 +1181,94 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="3" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>110</v>
+      </c>
+      <c r="B2">
+        <v>15</v>
+      </c>
+      <c r="C2">
+        <v>600</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:I37"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.42578125" style="7" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" style="7" customWidth="1"/>
@@ -1198,173 +1279,171 @@
     <col min="8" max="8" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="11" customFormat="1">
+      <c r="A1" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1"/>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="7">
+        <v>24</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="B2" s="9">
-        <v>24</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>37</v>
       </c>
       <c r="D2" s="7">
         <v>3</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="7">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9">
       <c r="A3" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="9">
+        <v>40</v>
+      </c>
+      <c r="B3" s="7">
         <v>24</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>36</v>
+      <c r="C3" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="D3" s="7">
         <v>5</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="7">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9">
       <c r="A4" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="9">
+        <v>40</v>
+      </c>
+      <c r="B4" s="7">
         <v>24</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>35</v>
+      <c r="C4" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="D4" s="7">
         <v>10</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9">
       <c r="A5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="9">
+        <v>40</v>
+      </c>
+      <c r="B5" s="7">
         <v>30</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>36</v>
+      <c r="C5" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="D5" s="7">
         <v>3</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="7">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="A6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="9">
+        <v>40</v>
+      </c>
+      <c r="B6" s="7">
         <v>30</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>35</v>
+      <c r="C6" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="D6" s="7">
         <v>5</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="7">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="A7" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="9">
+        <v>40</v>
+      </c>
+      <c r="B7" s="7">
         <v>30</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>33</v>
+      <c r="C7" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="D7" s="7">
         <v>10</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9">
       <c r="A8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="7">
+        <v>42</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="7">
+        <v>42</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="7">
+        <v>42</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="7">
+        <v>24</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="B8" s="9">
-        <v>42</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="9"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="9">
-        <v>42</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="9"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="9">
-        <v>42</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="9"/>
-      <c r="H10" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="9">
-        <v>24</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>37</v>
       </c>
       <c r="D11" s="7">
         <v>5</v>
@@ -1372,19 +1451,19 @@
       <c r="E11" s="7">
         <v>50</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="9">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9">
       <c r="A12" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="9">
+        <v>45</v>
+      </c>
+      <c r="B12" s="7">
         <v>24</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>36</v>
+      <c r="C12" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="D12" s="7">
         <v>10</v>
@@ -1393,15 +1472,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9">
       <c r="A13" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="9">
+        <v>45</v>
+      </c>
+      <c r="B13" s="7">
         <v>24</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>35</v>
+      <c r="C13" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="D13" s="7">
         <v>15</v>
@@ -1410,15 +1489,15 @@
         <v>150</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9">
       <c r="A14" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="9">
+        <v>45</v>
+      </c>
+      <c r="B14" s="7">
         <v>30</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>36</v>
+      <c r="C14" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="D14" s="7">
         <v>5</v>
@@ -1427,15 +1506,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="A15" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="9">
+        <v>45</v>
+      </c>
+      <c r="B15" s="7">
         <v>30</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>35</v>
+      <c r="C15" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="D15" s="7">
         <v>10</v>
@@ -1444,15 +1523,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9">
       <c r="A16" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="9">
+        <v>45</v>
+      </c>
+      <c r="B16" s="7">
         <v>30</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>33</v>
+      <c r="C16" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="D16" s="7">
         <v>15</v>
@@ -1461,48 +1540,48 @@
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="9">
+        <v>45</v>
+      </c>
+      <c r="B17" s="7">
         <v>42</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C17" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="9">
+        <v>45</v>
+      </c>
+      <c r="B18" s="7">
         <v>42</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C18" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="9">
+        <v>45</v>
+      </c>
+      <c r="B19" s="7">
         <v>42</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C19" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="9">
+        <v>46</v>
+      </c>
+      <c r="B20" s="7">
         <v>24</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>37</v>
+      <c r="C20" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="D20" s="7">
         <v>5</v>
@@ -1511,15 +1590,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5">
       <c r="A21" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="9">
+        <v>46</v>
+      </c>
+      <c r="B21" s="7">
         <v>24</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>36</v>
+      <c r="C21" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="D21" s="7">
         <v>7</v>
@@ -1528,15 +1607,15 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5">
       <c r="A22" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="9">
+        <v>46</v>
+      </c>
+      <c r="B22" s="7">
         <v>24</v>
       </c>
-      <c r="C22" s="9" t="s">
-        <v>35</v>
+      <c r="C22" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="D22" s="7">
         <v>10</v>
@@ -1545,15 +1624,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="9">
+        <v>46</v>
+      </c>
+      <c r="B23" s="7">
         <v>30</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>36</v>
+      <c r="C23" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="D23" s="7">
         <v>5</v>
@@ -1562,15 +1641,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5">
       <c r="A24" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="9">
+        <v>46</v>
+      </c>
+      <c r="B24" s="7">
         <v>30</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>35</v>
+      <c r="C24" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="D24" s="7">
         <v>7</v>
@@ -1579,15 +1658,15 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5">
       <c r="A25" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="9">
+        <v>46</v>
+      </c>
+      <c r="B25" s="7">
         <v>30</v>
       </c>
-      <c r="C25" s="9" t="s">
-        <v>33</v>
+      <c r="C25" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="D25" s="7">
         <v>10</v>
@@ -1596,48 +1675,48 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5">
       <c r="A26" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="9">
+        <v>46</v>
+      </c>
+      <c r="B26" s="7">
         <v>42</v>
       </c>
-      <c r="C26" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C26" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="9">
+        <v>46</v>
+      </c>
+      <c r="B27" s="7">
         <v>42</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C27" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="9">
+        <v>46</v>
+      </c>
+      <c r="B28" s="7">
         <v>42</v>
       </c>
-      <c r="C28" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C28" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="9">
+        <v>47</v>
+      </c>
+      <c r="B29" s="7">
         <v>24</v>
       </c>
-      <c r="C29" s="9" t="s">
-        <v>37</v>
+      <c r="C29" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="D29" s="7">
         <v>5</v>
@@ -1646,15 +1725,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5">
       <c r="A30" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="9">
+        <v>47</v>
+      </c>
+      <c r="B30" s="7">
         <v>24</v>
       </c>
-      <c r="C30" s="9" t="s">
-        <v>36</v>
+      <c r="C30" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="D30" s="7">
         <v>5</v>
@@ -1663,15 +1742,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5">
       <c r="A31" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="9">
+        <v>47</v>
+      </c>
+      <c r="B31" s="7">
         <v>24</v>
       </c>
-      <c r="C31" s="9" t="s">
-        <v>35</v>
+      <c r="C31" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="D31" s="7">
         <v>5</v>
@@ -1680,15 +1759,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5">
       <c r="A32" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B32" s="9">
+        <v>47</v>
+      </c>
+      <c r="B32" s="7">
         <v>30</v>
       </c>
-      <c r="C32" s="9" t="s">
-        <v>36</v>
+      <c r="C32" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="D32" s="7">
         <v>5</v>
@@ -1697,15 +1776,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5">
       <c r="A33" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33" s="9">
+        <v>47</v>
+      </c>
+      <c r="B33" s="7">
         <v>30</v>
       </c>
-      <c r="C33" s="9" t="s">
-        <v>35</v>
+      <c r="C33" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="D33" s="7">
         <v>5</v>
@@ -1714,15 +1793,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5">
       <c r="A34" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34" s="9">
+        <v>47</v>
+      </c>
+      <c r="B34" s="7">
         <v>30</v>
       </c>
-      <c r="C34" s="9" t="s">
-        <v>33</v>
+      <c r="C34" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="D34" s="7">
         <v>5</v>
@@ -1731,37 +1810,37 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5">
       <c r="A35" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="9">
+        <v>47</v>
+      </c>
+      <c r="B35" s="7">
         <v>42</v>
       </c>
-      <c r="C35" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C35" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="9">
+        <v>47</v>
+      </c>
+      <c r="B36" s="7">
         <v>42</v>
       </c>
-      <c r="C36" s="9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C36" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B37" s="9">
+        <v>47</v>
+      </c>
+      <c r="B37" s="7">
         <v>42</v>
       </c>
-      <c r="C37" s="9" t="s">
-        <v>33</v>
+      <c r="C37" s="7" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1771,9 +1850,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="5" width="15" customWidth="1"/>
@@ -1783,7 +1862,7 @@
     <col min="9" max="9" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="3" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1821,7 +1900,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1859,7 +1938,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1897,7 +1976,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1935,7 +2014,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1973,7 +2052,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2011,7 +2090,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2049,7 +2128,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -2087,7 +2166,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -2125,7 +2204,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -2163,7 +2242,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -2201,7 +2280,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -2239,7 +2318,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2277,7 +2356,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -2291,7 +2370,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -2305,7 +2384,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2319,7 +2398,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -2333,7 +2412,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -2347,7 +2426,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -2361,7 +2440,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -2375,7 +2454,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -2389,7 +2468,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -2403,7 +2482,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -2417,7 +2496,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -2455,7 +2534,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -2469,7 +2548,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12">
       <c r="A26" t="s">
         <v>15</v>
       </c>
@@ -2483,7 +2562,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12">
       <c r="A27" t="s">
         <v>15</v>
       </c>
@@ -2504,14 +2583,14 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -2528,7 +2607,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>12</v>
       </c>
@@ -2545,7 +2624,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>12</v>
       </c>
@@ -2562,7 +2641,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>12</v>
       </c>
@@ -2579,7 +2658,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>12</v>
       </c>
@@ -2596,7 +2675,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>12</v>
       </c>
@@ -2613,7 +2692,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>12</v>
       </c>
@@ -2627,7 +2706,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>12</v>
       </c>
@@ -2641,7 +2720,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>20</v>
       </c>
@@ -2655,7 +2734,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>20</v>
       </c>
@@ -2669,7 +2748,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>20</v>
       </c>
@@ -2683,7 +2762,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>20</v>
       </c>
@@ -2700,7 +2779,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>20</v>
       </c>
@@ -2717,7 +2796,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>20</v>
       </c>
@@ -2731,7 +2810,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>20</v>
       </c>
@@ -2745,7 +2824,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>20</v>
       </c>
@@ -2765,14 +2844,14 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C104"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -2783,7 +2862,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -2794,7 +2873,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -2805,7 +2884,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -2816,7 +2895,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -2827,7 +2906,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -2838,7 +2917,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -2849,7 +2928,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -2860,7 +2939,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -2871,7 +2950,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -2882,7 +2961,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -2893,7 +2972,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -2904,7 +2983,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -2915,7 +2994,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -2926,7 +3005,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -2937,7 +3016,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -2948,7 +3027,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -2959,7 +3038,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -2970,7 +3049,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -2981,7 +3060,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -2992,7 +3071,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -3003,7 +3082,7 @@
         <v>35.25</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -3014,7 +3093,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -3025,7 +3104,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -3036,7 +3115,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -3047,7 +3126,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -3058,7 +3137,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -3069,7 +3148,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>23</v>
       </c>
@@ -3080,7 +3159,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>23</v>
       </c>
@@ -3091,7 +3170,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>23</v>
       </c>
@@ -3102,7 +3181,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>23</v>
       </c>
@@ -3113,7 +3192,7 @@
         <v>20.350000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>23</v>
       </c>
@@ -3124,7 +3203,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>23</v>
       </c>
@@ -3135,7 +3214,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>23</v>
       </c>
@@ -3146,7 +3225,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>24</v>
       </c>
@@ -3157,7 +3236,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>24</v>
       </c>
@@ -3168,7 +3247,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>24</v>
       </c>
@@ -3179,7 +3258,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>24</v>
       </c>
@@ -3190,7 +3269,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>24</v>
       </c>
@@ -3201,7 +3280,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>24</v>
       </c>
@@ -3212,7 +3291,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>24</v>
       </c>
@@ -3223,7 +3302,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>24</v>
       </c>
@@ -3234,7 +3313,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>24</v>
       </c>
@@ -3245,7 +3324,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>24</v>
       </c>
@@ -3256,7 +3335,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>24</v>
       </c>
@@ -3267,7 +3346,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>24</v>
       </c>
@@ -3278,7 +3357,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -3289,7 +3368,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>24</v>
       </c>
@@ -3300,7 +3379,7 @@
         <v>48.5</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>25</v>
       </c>
@@ -3311,7 +3390,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>25</v>
       </c>
@@ -3322,7 +3401,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>25</v>
       </c>
@@ -3333,7 +3412,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>25</v>
       </c>
@@ -3344,7 +3423,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>25</v>
       </c>
@@ -3355,7 +3434,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
         <v>25</v>
       </c>
@@ -3366,7 +3445,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>25</v>
       </c>
@@ -3377,7 +3456,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3">
       <c r="A56" t="s">
         <v>25</v>
       </c>
@@ -3388,7 +3467,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3">
       <c r="A57" t="s">
         <v>25</v>
       </c>
@@ -3399,7 +3478,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3">
       <c r="A58" t="s">
         <v>25</v>
       </c>
@@ -3410,7 +3489,7 @@
         <v>27.75</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3">
       <c r="A59" t="s">
         <v>25</v>
       </c>
@@ -3421,7 +3500,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3">
       <c r="A60" t="s">
         <v>25</v>
       </c>
@@ -3432,7 +3511,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3">
       <c r="A61" t="s">
         <v>25</v>
       </c>
@@ -3443,7 +3522,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3">
       <c r="A62" t="s">
         <v>25</v>
       </c>
@@ -3454,7 +3533,7 @@
         <v>66.5</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3">
       <c r="A63" t="s">
         <v>26</v>
       </c>
@@ -3462,7 +3541,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3">
       <c r="A64" t="s">
         <v>26</v>
       </c>
@@ -3473,7 +3552,7 @@
         <v>22.25</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3">
       <c r="A65" t="s">
         <v>26</v>
       </c>
@@ -3484,7 +3563,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3">
       <c r="A66" t="s">
         <v>26</v>
       </c>
@@ -3495,7 +3574,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3">
       <c r="A67" t="s">
         <v>26</v>
       </c>
@@ -3506,7 +3585,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3">
       <c r="A68" t="s">
         <v>26</v>
       </c>
@@ -3517,7 +3596,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3">
       <c r="A69" t="s">
         <v>26</v>
       </c>
@@ -3528,7 +3607,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3">
       <c r="A70" t="s">
         <v>26</v>
       </c>
@@ -3539,7 +3618,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3">
       <c r="A71" t="s">
         <v>26</v>
       </c>
@@ -3550,7 +3629,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3">
       <c r="A72" t="s">
         <v>26</v>
       </c>
@@ -3561,7 +3640,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3">
       <c r="A73" t="s">
         <v>26</v>
       </c>
@@ -3572,7 +3651,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3">
       <c r="A74" t="s">
         <v>26</v>
       </c>
@@ -3583,7 +3662,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3">
       <c r="A75" t="s">
         <v>26</v>
       </c>
@@ -3594,7 +3673,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3">
       <c r="A76" t="s">
         <v>26</v>
       </c>
@@ -3605,7 +3684,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3">
       <c r="A77" t="s">
         <v>26</v>
       </c>
@@ -3616,7 +3695,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3">
       <c r="A78" t="s">
         <v>26</v>
       </c>
@@ -3627,7 +3706,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3">
       <c r="A79" t="s">
         <v>27</v>
       </c>
@@ -3635,7 +3714,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3">
       <c r="A80" t="s">
         <v>27</v>
       </c>
@@ -3643,7 +3722,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3">
       <c r="A81" t="s">
         <v>27</v>
       </c>
@@ -3654,7 +3733,7 @@
         <v>43.5</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3">
       <c r="A82" t="s">
         <v>27</v>
       </c>
@@ -3665,7 +3744,7 @@
         <v>43.5</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3">
       <c r="A83" t="s">
         <v>27</v>
       </c>
@@ -3676,7 +3755,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3">
       <c r="A84" t="s">
         <v>27</v>
       </c>
@@ -3687,7 +3766,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3">
       <c r="A85" t="s">
         <v>27</v>
       </c>
@@ -3698,7 +3777,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3">
       <c r="A86" t="s">
         <v>27</v>
       </c>
@@ -3709,7 +3788,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3">
       <c r="A87" t="s">
         <v>27</v>
       </c>
@@ -3720,7 +3799,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3">
       <c r="A88" t="s">
         <v>27</v>
       </c>
@@ -3731,7 +3810,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3">
       <c r="A89" t="s">
         <v>27</v>
       </c>
@@ -3742,7 +3821,7 @@
         <v>64.5</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3">
       <c r="A90" t="s">
         <v>27</v>
       </c>
@@ -3753,7 +3832,7 @@
         <v>75.5</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3">
       <c r="A91" t="s">
         <v>27</v>
       </c>
@@ -3764,7 +3843,7 @@
         <v>93.5</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3">
       <c r="A92" t="s">
         <v>27</v>
       </c>
@@ -3775,7 +3854,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3">
       <c r="A93" t="s">
         <v>27</v>
       </c>
@@ -3786,7 +3865,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3">
       <c r="A94" t="s">
         <v>27</v>
       </c>
@@ -3797,7 +3876,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3">
       <c r="A95" t="s">
         <v>27</v>
       </c>
@@ -3808,7 +3887,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3">
       <c r="A96" t="s">
         <v>27</v>
       </c>
@@ -3819,7 +3898,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3">
       <c r="A97" t="s">
         <v>27</v>
       </c>
@@ -3830,7 +3909,7 @@
         <v>266.5</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3">
       <c r="A98" t="s">
         <v>27</v>
       </c>
@@ -3841,7 +3920,7 @@
         <v>266.5</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3">
       <c r="A99" t="s">
         <v>27</v>
       </c>
@@ -3852,7 +3931,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3">
       <c r="A100" t="s">
         <v>27</v>
       </c>
@@ -3863,7 +3942,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3">
       <c r="A101" t="s">
         <v>27</v>
       </c>
@@ -3874,7 +3953,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3">
       <c r="A102" t="s">
         <v>27</v>
       </c>
@@ -3885,7 +3964,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3">
       <c r="A103" t="s">
         <v>27</v>
       </c>
@@ -3896,7 +3975,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3">
       <c r="A104" t="s">
         <v>27</v>
       </c>
@@ -3913,14 +3992,114 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B74891D3-DF2E-486D-BD3A-B1514405FBFB}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="3" customFormat="1">
+      <c r="A1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>195</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EDBF1AD-54D8-4F40-BE52-F36B1C78B207}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -3934,7 +4113,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>16</v>
       </c>
@@ -3948,7 +4127,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>18</v>
       </c>
@@ -3962,7 +4141,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>24</v>
       </c>
@@ -3974,267 +4153,6 @@
       </c>
       <c r="D4">
         <v>75</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="4" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>25</v>
-      </c>
-      <c r="B2">
-        <v>25</v>
-      </c>
-      <c r="C2">
-        <v>200</v>
-      </c>
-      <c r="D2">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>25</v>
-      </c>
-      <c r="B3">
-        <v>25</v>
-      </c>
-      <c r="C3">
-        <v>250</v>
-      </c>
-      <c r="D3">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>25</v>
-      </c>
-      <c r="B4">
-        <v>25</v>
-      </c>
-      <c r="C4">
-        <v>300</v>
-      </c>
-      <c r="D4">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>25</v>
-      </c>
-      <c r="B5">
-        <v>25</v>
-      </c>
-      <c r="C5">
-        <v>350</v>
-      </c>
-      <c r="D5">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>25</v>
-      </c>
-      <c r="B6">
-        <v>25</v>
-      </c>
-      <c r="C6">
-        <v>400</v>
-      </c>
-      <c r="D6">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>32</v>
-      </c>
-      <c r="B7">
-        <v>32</v>
-      </c>
-      <c r="C7">
-        <v>200</v>
-      </c>
-      <c r="D7">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>32</v>
-      </c>
-      <c r="B8">
-        <v>32</v>
-      </c>
-      <c r="C8">
-        <v>250</v>
-      </c>
-      <c r="D8">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>32</v>
-      </c>
-      <c r="B9">
-        <v>32</v>
-      </c>
-      <c r="C9">
-        <v>300</v>
-      </c>
-      <c r="D9">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>32</v>
-      </c>
-      <c r="B10">
-        <v>32</v>
-      </c>
-      <c r="C10">
-        <v>350</v>
-      </c>
-      <c r="D10">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>32</v>
-      </c>
-      <c r="B11">
-        <v>32</v>
-      </c>
-      <c r="C11">
-        <v>400</v>
-      </c>
-      <c r="D11">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>50</v>
-      </c>
-      <c r="B12">
-        <v>50</v>
-      </c>
-      <c r="C12">
-        <v>200</v>
-      </c>
-      <c r="D12">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>50</v>
-      </c>
-      <c r="B13">
-        <v>50</v>
-      </c>
-      <c r="C13">
-        <v>250</v>
-      </c>
-      <c r="D13">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>50</v>
-      </c>
-      <c r="B14">
-        <v>50</v>
-      </c>
-      <c r="C14">
-        <v>300</v>
-      </c>
-      <c r="D14">
-        <v>1160</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>50</v>
-      </c>
-      <c r="B15">
-        <v>50</v>
-      </c>
-      <c r="C15">
-        <v>350</v>
-      </c>
-      <c r="D15">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>50</v>
-      </c>
-      <c r="B16">
-        <v>50</v>
-      </c>
-      <c r="C16">
-        <v>400</v>
-      </c>
-      <c r="D16">
-        <v>1380</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="3" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -4243,22 +4161,235 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="3" width="12" customWidth="1"/>
+    <col min="1" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>25</v>
+      </c>
+      <c r="B2">
+        <v>25</v>
+      </c>
+      <c r="C2">
+        <v>200</v>
+      </c>
+      <c r="D2">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>25</v>
+      </c>
+      <c r="B3">
+        <v>25</v>
+      </c>
+      <c r="C3">
+        <v>250</v>
+      </c>
+      <c r="D3">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>25</v>
+      </c>
+      <c r="B4">
+        <v>25</v>
+      </c>
+      <c r="C4">
+        <v>300</v>
+      </c>
+      <c r="D4">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>25</v>
+      </c>
+      <c r="B5">
+        <v>25</v>
+      </c>
+      <c r="C5">
+        <v>350</v>
+      </c>
+      <c r="D5">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>25</v>
+      </c>
+      <c r="B6">
+        <v>25</v>
+      </c>
+      <c r="C6">
+        <v>400</v>
+      </c>
+      <c r="D6">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>32</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>200</v>
+      </c>
+      <c r="D7">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>32</v>
+      </c>
+      <c r="B8">
+        <v>32</v>
+      </c>
+      <c r="C8">
+        <v>250</v>
+      </c>
+      <c r="D8">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>32</v>
+      </c>
+      <c r="C9">
+        <v>300</v>
+      </c>
+      <c r="D9">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>32</v>
+      </c>
+      <c r="B10">
+        <v>32</v>
+      </c>
+      <c r="C10">
+        <v>350</v>
+      </c>
+      <c r="D10">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>32</v>
+      </c>
+      <c r="B11">
+        <v>32</v>
+      </c>
+      <c r="C11">
+        <v>400</v>
+      </c>
+      <c r="D11">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>50</v>
+      </c>
+      <c r="B12">
+        <v>50</v>
+      </c>
+      <c r="C12">
+        <v>200</v>
+      </c>
+      <c r="D12">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>50</v>
+      </c>
+      <c r="B13">
+        <v>50</v>
+      </c>
+      <c r="C13">
+        <v>250</v>
+      </c>
+      <c r="D13">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>50</v>
+      </c>
+      <c r="B14">
+        <v>50</v>
+      </c>
+      <c r="C14">
+        <v>300</v>
+      </c>
+      <c r="D14">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15">
+        <v>50</v>
+      </c>
+      <c r="B15">
+        <v>50</v>
+      </c>
+      <c r="C15">
+        <v>350</v>
+      </c>
+      <c r="D15">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16">
+        <v>50</v>
+      </c>
+      <c r="B16">
+        <v>50</v>
+      </c>
+      <c r="C16">
+        <v>400</v>
+      </c>
+      <c r="D16">
+        <v>1380</v>
       </c>
     </row>
   </sheetData>
@@ -4267,33 +4398,22 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>110</v>
-      </c>
-      <c r="B2">
-        <v>15</v>
-      </c>
-      <c r="C2">
-        <v>600</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Standard_Chart_filled.xlsx
+++ b/Standard_Chart_filled.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30431"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30502"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{354A867E-E3E9-4EF4-A70F-773F932181E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F6958FD-5C68-4951-9B82-8CA3EC6268AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="7455" firstSheet="10" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="7455" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GuidePin" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,16 @@
     <sheet name="ReturnPin" sheetId="3" r:id="rId3"/>
     <sheet name="Bolts" sheetId="4" r:id="rId4"/>
     <sheet name="Cavityhousingdrilling" sheetId="12" r:id="rId5"/>
-    <sheet name="CavityInsertDrilling" sheetId="13" r:id="rId6"/>
-    <sheet name="DowellingSleeve" sheetId="5" r:id="rId7"/>
-    <sheet name="HookStrip" sheetId="6" r:id="rId8"/>
-    <sheet name="EjectorGuidePin" sheetId="7" r:id="rId9"/>
-    <sheet name="EjectorGuideBush" sheetId="8" r:id="rId10"/>
-    <sheet name="LocatingRing" sheetId="9" r:id="rId11"/>
-    <sheet name="PlateThickness" sheetId="10" r:id="rId12"/>
-    <sheet name="BoringProcess" sheetId="11" r:id="rId13"/>
+    <sheet name="SpacerBlocksCosting" sheetId="15" r:id="rId6"/>
+    <sheet name="BoltStandards" sheetId="14" r:id="rId7"/>
+    <sheet name="CavityInsertDrilling" sheetId="13" r:id="rId8"/>
+    <sheet name="DowellingSleeve" sheetId="5" r:id="rId9"/>
+    <sheet name="HookStrip" sheetId="6" r:id="rId10"/>
+    <sheet name="EjectorGuidePin" sheetId="7" r:id="rId11"/>
+    <sheet name="EjectorGuideBush" sheetId="8" r:id="rId12"/>
+    <sheet name="LocatingRing" sheetId="9" r:id="rId13"/>
+    <sheet name="PlateThickness" sheetId="10" r:id="rId14"/>
+    <sheet name="BoringProcess" sheetId="11" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -48,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="57">
   <si>
     <t>Type</t>
   </si>
@@ -149,6 +151,39 @@
     <t>38-48</t>
   </si>
   <si>
+    <t>30-48</t>
+  </si>
+  <si>
+    <t>48-60</t>
+  </si>
+  <si>
+    <t>60-80</t>
+  </si>
+  <si>
+    <t>80-100</t>
+  </si>
+  <si>
+    <t>Bolt Dia</t>
+  </si>
+  <si>
+    <t>Clearance hole dia</t>
+  </si>
+  <si>
+    <t>Counter bore dia</t>
+  </si>
+  <si>
+    <t>Counter bore depth</t>
+  </si>
+  <si>
+    <t>M20</t>
+  </si>
+  <si>
+    <t>Outer dia</t>
+  </si>
+  <si>
+    <t>Inner dia</t>
+  </si>
+  <si>
     <t>W</t>
   </si>
   <si>
@@ -174,12 +209,6 @@
   </si>
   <si>
     <t>16-24</t>
-  </si>
-  <si>
-    <t>30-48</t>
-  </si>
-  <si>
-    <t>48-60</t>
   </si>
   <si>
     <t>Setting cost</t>
@@ -267,7 +296,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -290,6 +319,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1157,6 +1188,267 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="4" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>25</v>
+      </c>
+      <c r="B2">
+        <v>25</v>
+      </c>
+      <c r="C2">
+        <v>200</v>
+      </c>
+      <c r="D2">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>25</v>
+      </c>
+      <c r="B3">
+        <v>25</v>
+      </c>
+      <c r="C3">
+        <v>250</v>
+      </c>
+      <c r="D3">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>25</v>
+      </c>
+      <c r="B4">
+        <v>25</v>
+      </c>
+      <c r="C4">
+        <v>300</v>
+      </c>
+      <c r="D4">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>25</v>
+      </c>
+      <c r="B5">
+        <v>25</v>
+      </c>
+      <c r="C5">
+        <v>350</v>
+      </c>
+      <c r="D5">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>25</v>
+      </c>
+      <c r="B6">
+        <v>25</v>
+      </c>
+      <c r="C6">
+        <v>400</v>
+      </c>
+      <c r="D6">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>32</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>200</v>
+      </c>
+      <c r="D7">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>32</v>
+      </c>
+      <c r="B8">
+        <v>32</v>
+      </c>
+      <c r="C8">
+        <v>250</v>
+      </c>
+      <c r="D8">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>32</v>
+      </c>
+      <c r="C9">
+        <v>300</v>
+      </c>
+      <c r="D9">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>32</v>
+      </c>
+      <c r="B10">
+        <v>32</v>
+      </c>
+      <c r="C10">
+        <v>350</v>
+      </c>
+      <c r="D10">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>32</v>
+      </c>
+      <c r="B11">
+        <v>32</v>
+      </c>
+      <c r="C11">
+        <v>400</v>
+      </c>
+      <c r="D11">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>50</v>
+      </c>
+      <c r="B12">
+        <v>50</v>
+      </c>
+      <c r="C12">
+        <v>200</v>
+      </c>
+      <c r="D12">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>50</v>
+      </c>
+      <c r="B13">
+        <v>50</v>
+      </c>
+      <c r="C13">
+        <v>250</v>
+      </c>
+      <c r="D13">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>50</v>
+      </c>
+      <c r="B14">
+        <v>50</v>
+      </c>
+      <c r="C14">
+        <v>300</v>
+      </c>
+      <c r="D14">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15">
+        <v>50</v>
+      </c>
+      <c r="B15">
+        <v>50</v>
+      </c>
+      <c r="C15">
+        <v>350</v>
+      </c>
+      <c r="D15">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16">
+        <v>50</v>
+      </c>
+      <c r="B16">
+        <v>50</v>
+      </c>
+      <c r="C16">
+        <v>400</v>
+      </c>
+      <c r="D16">
+        <v>1380</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="3" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1180,7 +1472,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1193,10 +1485,10 @@
         <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1215,9 +1507,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1260,12 +1552,22 @@
         <v>76</v>
       </c>
     </row>
+    <row r="9" spans="1:1">
+      <c r="A9">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1281,16 +1583,16 @@
   <sheetData>
     <row r="1" spans="1:9" s="11" customFormat="1">
       <c r="A1" s="11" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C1" s="11" t="s">
         <v>29</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E1" s="11" t="s">
         <v>30</v>
@@ -1299,13 +1601,13 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="7" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B2" s="7">
         <v>24</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D2" s="7">
         <v>3</v>
@@ -1316,7 +1618,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="7" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B3" s="7">
         <v>24</v>
@@ -1333,13 +1635,13 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="7" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B4" s="7">
         <v>24</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D4" s="7">
         <v>10</v>
@@ -1350,7 +1652,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="7" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B5" s="7">
         <v>30</v>
@@ -1367,13 +1669,13 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="7" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B6" s="7">
         <v>30</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D6" s="7">
         <v>5</v>
@@ -1384,13 +1686,13 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="7" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B7" s="7">
         <v>30</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D7" s="7">
         <v>10</v>
@@ -1401,7 +1703,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="7" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B8" s="7">
         <v>42</v>
@@ -1412,38 +1714,38 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="7" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B9" s="7">
         <v>42</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="7" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B10" s="7">
         <v>42</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="7" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B11" s="7">
         <v>24</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D11" s="7">
         <v>5</v>
@@ -1457,7 +1759,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="7" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B12" s="7">
         <v>24</v>
@@ -1474,13 +1776,13 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="7" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B13" s="7">
         <v>24</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D13" s="7">
         <v>15</v>
@@ -1491,7 +1793,7 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="7" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B14" s="7">
         <v>30</v>
@@ -1508,13 +1810,13 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="7" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B15" s="7">
         <v>30</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D15" s="7">
         <v>10</v>
@@ -1525,13 +1827,13 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="7" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B16" s="7">
         <v>30</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D16" s="7">
         <v>15</v>
@@ -1542,7 +1844,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="7" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B17" s="7">
         <v>42</v>
@@ -1553,35 +1855,35 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="7" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B18" s="7">
         <v>42</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="7" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B19" s="7">
         <v>42</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="7" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B20" s="7">
         <v>24</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D20" s="7">
         <v>5</v>
@@ -1592,7 +1894,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="7" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B21" s="7">
         <v>24</v>
@@ -1609,13 +1911,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="7" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B22" s="7">
         <v>24</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D22" s="7">
         <v>10</v>
@@ -1626,7 +1928,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="7" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B23" s="7">
         <v>30</v>
@@ -1643,13 +1945,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="7" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B24" s="7">
         <v>30</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D24" s="7">
         <v>7</v>
@@ -1660,13 +1962,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="7" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B25" s="7">
         <v>30</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D25" s="7">
         <v>10</v>
@@ -1677,7 +1979,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="7" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B26" s="7">
         <v>42</v>
@@ -1688,35 +1990,35 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="7" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B27" s="7">
         <v>42</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="7" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B28" s="7">
         <v>42</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="7" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B29" s="7">
         <v>24</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D29" s="7">
         <v>5</v>
@@ -1727,7 +2029,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="7" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B30" s="7">
         <v>24</v>
@@ -1744,13 +2046,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="7" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B31" s="7">
         <v>24</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D31" s="7">
         <v>5</v>
@@ -1761,7 +2063,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="7" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B32" s="7">
         <v>30</v>
@@ -1778,13 +2080,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="7" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B33" s="7">
         <v>30</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D33" s="7">
         <v>5</v>
@@ -1795,13 +2097,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="7" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B34" s="7">
         <v>30</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D34" s="7">
         <v>5</v>
@@ -1812,7 +2114,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="7" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B35" s="7">
         <v>42</v>
@@ -1823,24 +2125,24 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="7" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B36" s="7">
         <v>42</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="7" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B37" s="7">
         <v>42</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -4083,6 +4385,225 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F494F9A5-DEE4-459B-838E-E221E838E2BC}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="3" customFormat="1">
+      <c r="A1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6">
+        <v>630</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01B5BA2-867A-4433-BA93-D80922C363DE}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="13"/>
+    <col min="2" max="2" width="20.85546875" style="13" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" style="13" customWidth="1"/>
+    <col min="4" max="4" width="25.42578125" style="13" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="13" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="12" customFormat="1">
+      <c r="A1" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="13">
+        <v>3.5</v>
+      </c>
+      <c r="C2" s="13">
+        <v>6</v>
+      </c>
+      <c r="D2" s="13">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="C3" s="13">
+        <v>7</v>
+      </c>
+      <c r="D3" s="13">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="13">
+        <v>5.5</v>
+      </c>
+      <c r="C4" s="13">
+        <v>8.5</v>
+      </c>
+      <c r="D4" s="13">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="13">
+        <v>6.5</v>
+      </c>
+      <c r="C5" s="13">
+        <v>11</v>
+      </c>
+      <c r="D5" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="13">
+        <v>9</v>
+      </c>
+      <c r="C6" s="13">
+        <v>13</v>
+      </c>
+      <c r="D6" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="13">
+        <v>11</v>
+      </c>
+      <c r="C7" s="13">
+        <v>18</v>
+      </c>
+      <c r="D7" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="13">
+        <v>14</v>
+      </c>
+      <c r="C8" s="13">
+        <v>20</v>
+      </c>
+      <c r="D8" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="13">
+        <v>18</v>
+      </c>
+      <c r="C9" s="13">
+        <v>26</v>
+      </c>
+      <c r="D9" s="13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="13">
+        <v>22</v>
+      </c>
+      <c r="C10" s="13">
+        <v>32</v>
+      </c>
+      <c r="D10" s="13">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EDBF1AD-54D8-4F40-BE52-F36B1C78B207}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4091,20 +4612,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="4" width="12" customWidth="1"/>
+    <col min="1" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
@@ -4153,267 +4676,6 @@
       </c>
       <c r="D4">
         <v>75</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="4" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
-        <v>25</v>
-      </c>
-      <c r="B2">
-        <v>25</v>
-      </c>
-      <c r="C2">
-        <v>200</v>
-      </c>
-      <c r="D2">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
-        <v>25</v>
-      </c>
-      <c r="B3">
-        <v>25</v>
-      </c>
-      <c r="C3">
-        <v>250</v>
-      </c>
-      <c r="D3">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
-        <v>25</v>
-      </c>
-      <c r="B4">
-        <v>25</v>
-      </c>
-      <c r="C4">
-        <v>300</v>
-      </c>
-      <c r="D4">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5">
-        <v>25</v>
-      </c>
-      <c r="B5">
-        <v>25</v>
-      </c>
-      <c r="C5">
-        <v>350</v>
-      </c>
-      <c r="D5">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6">
-        <v>25</v>
-      </c>
-      <c r="B6">
-        <v>25</v>
-      </c>
-      <c r="C6">
-        <v>400</v>
-      </c>
-      <c r="D6">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7">
-        <v>32</v>
-      </c>
-      <c r="B7">
-        <v>32</v>
-      </c>
-      <c r="C7">
-        <v>200</v>
-      </c>
-      <c r="D7">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8">
-        <v>32</v>
-      </c>
-      <c r="B8">
-        <v>32</v>
-      </c>
-      <c r="C8">
-        <v>250</v>
-      </c>
-      <c r="D8">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9">
-        <v>32</v>
-      </c>
-      <c r="B9">
-        <v>32</v>
-      </c>
-      <c r="C9">
-        <v>300</v>
-      </c>
-      <c r="D9">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10">
-        <v>32</v>
-      </c>
-      <c r="B10">
-        <v>32</v>
-      </c>
-      <c r="C10">
-        <v>350</v>
-      </c>
-      <c r="D10">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11">
-        <v>32</v>
-      </c>
-      <c r="B11">
-        <v>32</v>
-      </c>
-      <c r="C11">
-        <v>400</v>
-      </c>
-      <c r="D11">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12">
-        <v>50</v>
-      </c>
-      <c r="B12">
-        <v>50</v>
-      </c>
-      <c r="C12">
-        <v>200</v>
-      </c>
-      <c r="D12">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13">
-        <v>50</v>
-      </c>
-      <c r="B13">
-        <v>50</v>
-      </c>
-      <c r="C13">
-        <v>250</v>
-      </c>
-      <c r="D13">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14">
-        <v>50</v>
-      </c>
-      <c r="B14">
-        <v>50</v>
-      </c>
-      <c r="C14">
-        <v>300</v>
-      </c>
-      <c r="D14">
-        <v>1160</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15">
-        <v>50</v>
-      </c>
-      <c r="B15">
-        <v>50</v>
-      </c>
-      <c r="C15">
-        <v>350</v>
-      </c>
-      <c r="D15">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16">
-        <v>50</v>
-      </c>
-      <c r="B16">
-        <v>50</v>
-      </c>
-      <c r="C16">
-        <v>400</v>
-      </c>
-      <c r="D16">
-        <v>1380</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="3" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Standard_Chart_filled.xlsx
+++ b/Standard_Chart_filled.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F6958FD-5C68-4951-9B82-8CA3EC6268AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8478EEE7-66C9-426E-9F83-2D4663A47E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="7455" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="7455" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GuidePin" sheetId="1" r:id="rId1"/>
@@ -18,16 +18,18 @@
     <sheet name="ReturnPin" sheetId="3" r:id="rId3"/>
     <sheet name="Bolts" sheetId="4" r:id="rId4"/>
     <sheet name="Cavityhousingdrilling" sheetId="12" r:id="rId5"/>
-    <sheet name="SpacerBlocksCosting" sheetId="15" r:id="rId6"/>
-    <sheet name="BoltStandards" sheetId="14" r:id="rId7"/>
-    <sheet name="CavityInsertDrilling" sheetId="13" r:id="rId8"/>
-    <sheet name="DowellingSleeve" sheetId="5" r:id="rId9"/>
-    <sheet name="HookStrip" sheetId="6" r:id="rId10"/>
-    <sheet name="EjectorGuidePin" sheetId="7" r:id="rId11"/>
-    <sheet name="EjectorGuideBush" sheetId="8" r:id="rId12"/>
-    <sheet name="LocatingRing" sheetId="9" r:id="rId13"/>
-    <sheet name="PlateThickness" sheetId="10" r:id="rId14"/>
-    <sheet name="BoringProcess" sheetId="11" r:id="rId15"/>
+    <sheet name="PunchHousingDrilling" sheetId="16" r:id="rId6"/>
+    <sheet name="PunchBackPlate" sheetId="17" r:id="rId7"/>
+    <sheet name="SpacerBlocksCosting" sheetId="15" r:id="rId8"/>
+    <sheet name="BoltStandards" sheetId="14" r:id="rId9"/>
+    <sheet name="CavityInsertDrilling" sheetId="13" r:id="rId10"/>
+    <sheet name="DowellingSleeve" sheetId="5" r:id="rId11"/>
+    <sheet name="HookStrip" sheetId="6" r:id="rId12"/>
+    <sheet name="EjectorGuidePin" sheetId="7" r:id="rId13"/>
+    <sheet name="EjectorGuideBush" sheetId="8" r:id="rId14"/>
+    <sheet name="LocatingRing" sheetId="9" r:id="rId15"/>
+    <sheet name="PlateThickness" sheetId="10" r:id="rId16"/>
+    <sheet name="BoringProcess" sheetId="11" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -50,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="57">
   <si>
     <t>Type</t>
   </si>
@@ -151,10 +153,10 @@
     <t>38-48</t>
   </si>
   <si>
+    <t>48-60</t>
+  </si>
+  <si>
     <t>30-48</t>
-  </si>
-  <si>
-    <t>48-60</t>
   </si>
   <si>
     <t>60-80</t>
@@ -1188,6 +1190,86 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EDBF1AD-54D8-4F40-BE52-F36B1C78B207}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>16</v>
+      </c>
+      <c r="B2">
+        <v>11</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>18</v>
+      </c>
+      <c r="B3">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>24</v>
+      </c>
+      <c r="B4">
+        <v>18</v>
+      </c>
+      <c r="C4">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1424,7 +1506,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1448,7 +1530,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1472,7 +1554,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1507,7 +1589,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1567,7 +1649,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1641,7 +1723,7 @@
         <v>24</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" s="7">
         <v>10</v>
@@ -1675,7 +1757,7 @@
         <v>30</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" s="7">
         <v>5</v>
@@ -1692,7 +1774,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" s="7">
         <v>10</v>
@@ -1720,7 +1802,7 @@
         <v>42</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1731,7 +1813,7 @@
         <v>42</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>53</v>
@@ -1782,7 +1864,7 @@
         <v>24</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" s="7">
         <v>15</v>
@@ -1816,7 +1898,7 @@
         <v>30</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" s="7">
         <v>10</v>
@@ -1833,7 +1915,7 @@
         <v>30</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" s="7">
         <v>15</v>
@@ -1861,7 +1943,7 @@
         <v>42</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1872,7 +1954,7 @@
         <v>42</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1917,7 +1999,7 @@
         <v>24</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D22" s="7">
         <v>10</v>
@@ -1951,7 +2033,7 @@
         <v>30</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D24" s="7">
         <v>7</v>
@@ -1968,7 +2050,7 @@
         <v>30</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D25" s="7">
         <v>10</v>
@@ -1996,7 +2078,7 @@
         <v>42</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2007,7 +2089,7 @@
         <v>42</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2052,7 +2134,7 @@
         <v>24</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D31" s="7">
         <v>5</v>
@@ -2086,7 +2168,7 @@
         <v>30</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D33" s="7">
         <v>5</v>
@@ -2103,7 +2185,7 @@
         <v>30</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D34" s="7">
         <v>5</v>
@@ -2131,7 +2213,7 @@
         <v>42</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2142,7 +2224,7 @@
         <v>42</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -4385,6 +4467,246 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01B6612-4DA2-42AD-AA80-D1687F55FF15}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10">
+        <v>1090</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A49B8D45-7B4A-40C8-BF68-0BFDDF76E3E5}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10">
+        <v>1010</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F494F9A5-DEE4-459B-838E-E221E838E2BC}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4410,7 +4732,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3">
         <v>580</v>
@@ -4418,7 +4740,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4">
         <v>590</v>
@@ -4445,7 +4767,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01B5BA2-867A-4433-BA93-D80922C363DE}">
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4601,84 +4923,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EDBF1AD-54D8-4F40-BE52-F36B1C78B207}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
-        <v>16</v>
-      </c>
-      <c r="B2">
-        <v>11</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
-      </c>
-      <c r="D2">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
-        <v>18</v>
-      </c>
-      <c r="B3">
-        <v>13</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-      <c r="D3">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
-        <v>24</v>
-      </c>
-      <c r="B4">
-        <v>18</v>
-      </c>
-      <c r="C4">
-        <v>20</v>
-      </c>
-      <c r="D4">
-        <v>75</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>